--- a/docassemble/StudentEvaluations/data/sources/prs_complaint_interview_zh-Hans_rev1.xlsx
+++ b/docassemble/StudentEvaluations/data/sources/prs_complaint_interview_zh-Hans_rev1.xlsx
@@ -27199,7 +27199,7 @@
       </c>
       <c r="H616" s="3" t="inlineStr">
         <is>
-          <t>你的语言</t>
+          <t>您的语言</t>
         </is>
       </c>
     </row>
@@ -27239,7 +27239,7 @@
       </c>
       <c r="H617" s="3" t="inlineStr">
         <is>
-          <t>你最擅长哪种语言？</t>
+          <t>您最擅长哪种语言？</t>
         </is>
       </c>
     </row>
